--- a/src/assets/excel/BAI_template-payslip.xlsx
+++ b/src/assets/excel/BAI_template-payslip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\PROJECT\gbvh\gbvh\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B37EDF0-2F19-4293-A1A4-BE24F7458B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720B5037-4ADD-404C-9A0E-6AD26DBD1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
   </bookViews>
@@ -141,7 +141,7 @@
     <t>POTONGAN_BPJS</t>
   </si>
   <si>
-    <t>TOTAL_POTONGAN</t>
+    <t>POTONGAN_LAIN_LAIN</t>
   </si>
 </sst>
 </file>
